--- a/SAEN PEÑA/Noviembre/SAENZ_EXPENSAS-Noviembre.xlsx
+++ b/SAEN PEÑA/Noviembre/SAENZ_EXPENSAS-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7831841E-FF16-420E-AC41-75843587D663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84A95C9-DFB5-4910-B409-3890B0078AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="80">
   <si>
     <t>UF</t>
   </si>
@@ -238,27 +238,12 @@
     <t>PRESUPUESTO APROBADO - MANO DE OBRA GAS Y CLOACAS</t>
   </si>
   <si>
-    <t>Liquidacion mes de OCTUBRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Período OCTUBRE </t>
-  </si>
-  <si>
-    <t>Ladrisur - Arena, ladrillos, cemento</t>
-  </si>
-  <si>
-    <t>Matafuegos Fire - Recarga de matafuegos, manguera ABC p/ polvo - Cambio de marbete/precinto - P/ hidraulica matafuegos/ pres. manuales</t>
-  </si>
-  <si>
     <t>Julio Doartero - cambio de llave de gas vereda - Materiales y mano de obra</t>
   </si>
   <si>
     <t>Diferencia materiales (instalacion de gas)</t>
   </si>
   <si>
-    <t>Transportes villar - Camion 27/09</t>
-  </si>
-  <si>
     <t>Banchero Sanitarios Sa - compra acople</t>
   </si>
   <si>
@@ -269,6 +254,18 @@
   </si>
   <si>
     <t>Egreso de extraordinarias Sr. Julio Doartero - Resta abonar $500.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transportes villar </t>
+  </si>
+  <si>
+    <t>FEDERACION PATRONAL - SEGUROS</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de NOVIEMBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Período NOVIEMBRE </t>
   </si>
 </sst>
 </file>
@@ -283,7 +280,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,8 +388,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,6 +445,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1080,7 +1090,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1286,85 +1296,86 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="14" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="14" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="10" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1733,22 +1744,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1756,27 +1767,27 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1784,11 +1795,11 @@
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
       <c r="E7" s="24" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F7" s="98"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1796,44 +1807,44 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="97"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="121" t="s">
+      <c r="E11" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="121"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11" s="128"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="99"/>
       <c r="B12" s="99"/>
-      <c r="C12" s="144"/>
+      <c r="C12" s="122"/>
       <c r="D12" s="5"/>
       <c r="E12" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="143">
+      <c r="F12" s="121">
         <v>1355249.5529328201</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="97" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="144">
-        <v>35601</v>
+      <c r="C13" s="149">
+        <v>37185.11</v>
       </c>
       <c r="D13" s="36"/>
       <c r="E13" s="49" t="s">
@@ -1844,15 +1855,15 @@
         <v>125902.75973000002</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="99" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="144">
-        <v>31704.36</v>
+      <c r="C14" s="149">
+        <v>32096.82</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="49" t="s">
@@ -1860,72 +1871,76 @@
       </c>
       <c r="F14" s="50">
         <f>-(C42)</f>
-        <v>-1710814.9800000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1402151.3099999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="97" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="145">
+      <c r="C15" s="15">
         <v>32800</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="49" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F15" s="50">
         <v>4500000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="97"/>
-      <c r="B16" s="97"/>
-      <c r="C16" s="145"/>
-      <c r="E16" s="148" t="s">
-        <v>80</v>
+    <row r="16" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="152" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="152"/>
+      <c r="C16" s="154">
+        <v>8379</v>
+      </c>
+      <c r="E16" s="124" t="s">
+        <v>75</v>
       </c>
       <c r="F16" s="50">
         <v>-4000000</v>
       </c>
       <c r="G16" s="16"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="102"/>
       <c r="B17" s="103"/>
-      <c r="C17" s="146">
+      <c r="C17" s="123">
         <f>SUM(C12:C16)</f>
-        <v>100105.36</v>
+        <v>110460.93</v>
       </c>
       <c r="E17" s="51" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="118">
         <f>SUM(F12:F16)</f>
-        <v>270337.33266281988</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>579001.00266282074</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="101" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="97"/>
-      <c r="C18" s="147"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="5"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="97" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="145">
+        <v>79</v>
+      </c>
+      <c r="C19" s="15">
         <f xml:space="preserve"> 56588+56588*3%</f>
         <v>58285.64</v>
       </c>
@@ -1933,101 +1948,97 @@
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="122" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="123"/>
-      <c r="C20" s="145">
-        <v>45399.98</v>
+    <row r="20" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="150"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="148">
+        <v>23342.44</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="97" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="104"/>
-      <c r="C21" s="145">
-        <v>635000</v>
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="152"/>
+      <c r="B21" s="153"/>
+      <c r="C21" s="148">
+        <v>30226.92</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="97" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="104"/>
-      <c r="C22" s="145">
-        <v>118270</v>
+    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="153"/>
+      <c r="C22" s="148">
+        <v>200000</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="97" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B23" s="104"/>
-      <c r="C23" s="145">
-        <v>3918.62</v>
+      <c r="C23" s="15">
+        <v>220000</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="97" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B24" s="104"/>
-      <c r="C24" s="145">
+      <c r="C24" s="15">
         <v>176142.38</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="97" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B25" s="104"/>
-      <c r="C25" s="145">
+      <c r="C25" s="15">
         <v>363693</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="97" t="s">
         <v>76</v>
       </c>
       <c r="B26" s="104"/>
-      <c r="C26" s="144">
-        <v>210000</v>
+      <c r="C26" s="149">
+        <v>220000</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="97" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="104"/>
-      <c r="C27" s="144"/>
+      <c r="C27" s="122"/>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="97" t="s">
         <v>67</v>
       </c>
@@ -2037,32 +2048,32 @@
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="102"/>
       <c r="B29" s="103"/>
       <c r="C29" s="119">
         <f>SUM(C18:C28)</f>
-        <v>1610709.62</v>
+        <v>1291690.3799999999</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="47"/>
       <c r="G29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="40" t="s">
         <v>14</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="120">
         <f>+C29+C17</f>
-        <v>1710814.9800000002</v>
+        <v>1402151.3099999998</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
     </row>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="60" t="s">
         <v>27</v>
       </c>
@@ -2071,18 +2082,18 @@
       <c r="E31" s="19"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="37"/>
       <c r="B33" s="28"/>
       <c r="C33" s="46"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="44"/>
       <c r="B34" s="43"/>
       <c r="C34" s="45">
@@ -2090,7 +2101,7 @@
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="52"/>
       <c r="B35" s="53"/>
       <c r="C35" s="45">
@@ -2098,19 +2109,19 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="69"/>
       <c r="B36" s="70"/>
       <c r="C36" s="72"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="69"/>
       <c r="B37" s="76"/>
       <c r="C37" s="77"/>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="69"/>
       <c r="B38" s="75"/>
       <c r="C38" s="72">
@@ -2118,7 +2129,7 @@
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="54" t="s">
         <v>25</v>
       </c>
@@ -2128,91 +2139,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>59</v>
       </c>
-      <c r="C40" s="149">
+      <c r="C40" s="125">
         <f>C30-C28</f>
-        <v>1710814.9800000002</v>
+        <v>1402151.3099999998</v>
       </c>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="150">
+      <c r="C41" s="126">
         <f>+C30</f>
-        <v>1710814.9800000002</v>
+        <v>1402151.3099999998</v>
       </c>
       <c r="E41" s="100"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B42" s="55"/>
-      <c r="C42" s="151">
+      <c r="C42" s="127">
         <f>C40</f>
-        <v>1710814.9800000002</v>
+        <v>1402151.3099999998</v>
       </c>
       <c r="E42" s="16"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D50" s="16"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D51" s="16"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="19"/>
       <c r="B63" s="18"/>
       <c r="C63" s="20"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="18"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="18"/>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
@@ -2238,24 +2249,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
@@ -2277,10 +2288,10 @@
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de OCTUBRE</v>
+        <v>Liquidacion mes de NOVIEMBRE</v>
       </c>
       <c r="B2" s="64"/>
       <c r="C2" s="64"/>
@@ -2296,7 +2307,7 @@
       <c r="K2" s="67"/>
       <c r="L2" s="68"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2334,7 +2345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2364,7 +2375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2405,7 +2416,7 @@
         <v>288499.71267936</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2446,7 +2457,7 @@
         <v>299375.69391132006</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2463,7 +2474,7 @@
         <v>28787.131940000003</v>
       </c>
       <c r="F7" s="71">
-        <f t="shared" ref="F6:F10" si="2">E7</f>
+        <f t="shared" ref="F7:F10" si="2">E7</f>
         <v>28787.131940000003</v>
       </c>
       <c r="G7" s="58">
@@ -2490,7 +2501,7 @@
         <v>270650.92983600002</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2534,7 +2545,7 @@
         <v>338741.36604000005</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2578,7 +2589,7 @@
         <v>272361.74481600005</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2622,7 +2633,7 @@
         <v>301958.84397000005</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2665,24 +2676,24 @@
         <v>1771588.2912526804</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="124"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="129"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2702,21 +2713,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="106" t="s">
         <v>69</v>
       </c>
@@ -2725,13 +2736,13 @@
       <c r="D1" s="108"/>
       <c r="E1" s="109"/>
       <c r="F1" s="108"/>
-      <c r="G1" s="142">
+      <c r="G1" s="130">
         <v>4500000</v>
       </c>
-      <c r="H1" s="142"/>
+      <c r="H1" s="130"/>
       <c r="I1" s="110"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2760,7 +2771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2781,7 +2792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2813,7 +2824,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2845,7 +2856,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2877,7 +2888,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -2909,7 +2920,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -2941,7 +2952,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -2973,7 +2984,7 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
@@ -3004,21 +3015,21 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="124"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
@@ -3036,68 +3047,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="136" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="132"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="78"/>
       <c r="G1" s="78"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="133" t="s">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136">
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142">
         <v>565</v>
       </c>
-      <c r="E2" s="137"/>
+      <c r="E2" s="143"/>
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="138" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="138" t="s">
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="138" t="s">
+      <c r="C3" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="140" t="s">
+      <c r="D3" s="146" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="125" t="s">
+      <c r="E3" s="131" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="125" t="s">
+      <c r="F3" s="131" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="125" t="s">
+      <c r="G3" s="131" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="139"/>
-      <c r="B4" s="139"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="145"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="80">
         <v>1</v>
       </c>
@@ -3120,7 +3131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="80">
         <v>2</v>
       </c>
@@ -3143,7 +3154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="80">
         <v>3</v>
       </c>
@@ -3166,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="80">
         <v>4</v>
       </c>
@@ -3189,7 +3200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="80">
         <v>5</v>
       </c>
@@ -3212,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="85">
         <v>6</v>
       </c>
@@ -3235,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="90" t="s">
         <v>10</v>
       </c>
@@ -3254,12 +3265,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="127"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="129"/>
+    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="133"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="135"/>
       <c r="F12" s="78"/>
       <c r="G12" s="78"/>
     </row>

--- a/SAEN PEÑA/Noviembre/SAENZ_EXPENSAS-Noviembre.xlsx
+++ b/SAEN PEÑA/Noviembre/SAENZ_EXPENSAS-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84A95C9-DFB5-4910-B409-3890B0078AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19ACAA6-2E20-48D4-AFD0-55DCA2D59D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
   <si>
     <t>UF</t>
   </si>
@@ -238,34 +238,13 @@
     <t>PRESUPUESTO APROBADO - MANO DE OBRA GAS Y CLOACAS</t>
   </si>
   <si>
-    <t>Julio Doartero - cambio de llave de gas vereda - Materiales y mano de obra</t>
-  </si>
-  <si>
-    <t>Diferencia materiales (instalacion de gas)</t>
-  </si>
-  <si>
-    <t>Banchero Sanitarios Sa - compra acople</t>
-  </si>
-  <si>
-    <t>Banchero Sanitarios Sa - compra cupla, buje, codos varios, sellador, teflon</t>
-  </si>
-  <si>
-    <t>Ingeso de extraordinarias</t>
-  </si>
-  <si>
-    <t>Egreso de extraordinarias Sr. Julio Doartero - Resta abonar $500.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transportes villar </t>
-  </si>
-  <si>
-    <t>FEDERACION PATRONAL - SEGUROS</t>
-  </si>
-  <si>
     <t>Liquidacion mes de NOVIEMBRE</t>
   </si>
   <si>
     <t xml:space="preserve">Período NOVIEMBRE </t>
+  </si>
+  <si>
+    <t>Mercantil Andina Poliza. 1188950</t>
   </si>
 </sst>
 </file>
@@ -280,7 +259,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,15 +367,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,12 +417,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1090,7 +1056,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1298,10 +1264,6 @@
     <xf numFmtId="168" fontId="14" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="10" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1365,17 +1327,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1743,23 +1698,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1767,27 +1722,27 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1795,11 +1750,11 @@
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
       <c r="E7" s="24" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F7" s="98"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1807,24 +1762,24 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="97"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="128"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="126"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="99"/>
       <c r="B12" s="99"/>
       <c r="C12" s="122"/>
@@ -1833,17 +1788,17 @@
         <v>48</v>
       </c>
       <c r="F12" s="121">
-        <v>1355249.5529328201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>270337.33266281988</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="149">
+      <c r="C13" s="105">
         <v>37185.11</v>
       </c>
       <c r="D13" s="36"/>
@@ -1852,17 +1807,17 @@
       </c>
       <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>125902.75973000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1483168.0599513201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="99" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="105">
         <v>32096.82</v>
       </c>
       <c r="D14" s="5"/>
@@ -1870,368 +1825,290 @@
         <v>22</v>
       </c>
       <c r="F14" s="50">
-        <f>-(C42)</f>
-        <v>-1402151.3099999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <f>-(C36)</f>
+        <v>-197552.56999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="71">
         <v>32800</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="50">
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="152" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="152"/>
-      <c r="C16" s="154">
-        <v>8379</v>
-      </c>
-      <c r="E16" s="124" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="50">
-        <v>-4000000</v>
-      </c>
-      <c r="G16" s="16"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="123">
-        <f>SUM(C12:C16)</f>
-        <v>110460.93</v>
-      </c>
-      <c r="E17" s="51" t="s">
+      <c r="E15" s="49"/>
+      <c r="F15" s="50"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="97"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="50"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="71">
+        <v>37185</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="146">
+        <f>SUM(C12:C17)</f>
+        <v>139266.93</v>
+      </c>
+      <c r="E18" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="118">
-        <f>SUM(F12:F16)</f>
-        <v>579001.00266282074</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="101" t="s">
+      <c r="F18" s="118">
+        <f>SUM(F12:F15)</f>
+        <v>1555952.8226141399</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-    </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="97" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="104" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="15">
-        <f xml:space="preserve"> 56588+56588*3%</f>
-        <v>58285.64</v>
-      </c>
+      <c r="B19" s="97"/>
+      <c r="C19" s="147"/>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="150"/>
-      <c r="B20" s="151"/>
-      <c r="C20" s="148">
-        <v>23342.44</v>
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="97" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="71">
+        <f xml:space="preserve"> 56588+56588*3%</f>
+        <v>58285.64</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="152"/>
-      <c r="B21" s="153"/>
-      <c r="C21" s="148">
-        <v>30226.92</v>
-      </c>
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="104"/>
+      <c r="C21" s="122"/>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="152" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="153"/>
-      <c r="C22" s="148">
-        <v>200000</v>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="104"/>
+      <c r="C22" s="105">
+        <f>400000-197552.6</f>
+        <v>202447.4</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="97" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="104"/>
-      <c r="C23" s="15">
-        <v>220000</v>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="102"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="119">
+        <f>SUM(C19:C22)</f>
+        <v>260733.03999999998</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-    </row>
-    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="104"/>
-      <c r="C24" s="15">
-        <v>176142.38</v>
+      <c r="E23" s="5"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="120">
+        <f>+C23+C18</f>
+        <v>399999.97</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="97" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="104"/>
-      <c r="C25" s="15">
-        <v>363693</v>
-      </c>
-      <c r="D25" s="5"/>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="73"/>
+      <c r="C25" s="74"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="97" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="104"/>
-      <c r="C26" s="149">
-        <v>220000</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="97" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="104"/>
-      <c r="C27" s="122"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="97" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="104"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="102"/>
-      <c r="B29" s="103"/>
-      <c r="C29" s="119">
-        <f>SUM(C18:C28)</f>
-        <v>1291690.3799999999</v>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="120">
-        <f>+C29+C17</f>
-        <v>1402151.3099999998</v>
-      </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="20"/>
-    </row>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="60" t="s">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="73"/>
-      <c r="C31" s="74"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="20"/>
-    </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="46"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="44"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="45">
-        <v>0</v>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="46"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="45">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="52"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="45">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="69"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="72"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="69"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="69"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="72">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="55"/>
+      <c r="C33" s="56">
+        <f>SUM(C28:C32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="123">
+        <f>C24-C22</f>
+        <v>197552.56999999998</v>
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="52"/>
-      <c r="B35" s="53"/>
-      <c r="C35" s="45">
-        <v>0</v>
-      </c>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="124">
+        <f>+C24</f>
+        <v>399999.97</v>
+      </c>
+      <c r="E35" s="100"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="69"/>
-      <c r="B36" s="70"/>
-      <c r="C36" s="72"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="69"/>
-      <c r="B37" s="76"/>
-      <c r="C37" s="77"/>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="69"/>
-      <c r="B38" s="75"/>
-      <c r="C38" s="72">
-        <v>0</v>
-      </c>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="56">
-        <f>SUM(C34:C38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="125">
-        <f>C30-C28</f>
-        <v>1402151.3099999998</v>
-      </c>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="126">
-        <f>+C30</f>
-        <v>1402151.3099999998</v>
-      </c>
-      <c r="E41" s="100"/>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="54" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="127">
-        <f>C40</f>
-        <v>1402151.3099999998</v>
-      </c>
+      <c r="B36" s="55"/>
+      <c r="C36" s="125">
+        <f>C34</f>
+        <v>197552.56999999998</v>
+      </c>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D50" s="16"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D51" s="16"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="16"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="16"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="19"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="20"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="18"/>
       <c r="B63" s="18"/>
-      <c r="C63" s="20"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C63" s="18"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="18"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="18"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2249,24 +2126,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
@@ -2284,11 +2161,11 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="62">
-        <v>1710814.9800000002</v>
+        <v>400000</v>
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de NOVIEMBRE</v>
@@ -2307,7 +2184,7 @@
       <c r="K2" s="67"/>
       <c r="L2" s="68"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2345,7 +2222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2375,7 +2252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2389,23 +2266,23 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>27513.365040000001</v>
+        <v>288499.71267936</v>
       </c>
       <c r="F5" s="71"/>
       <c r="G5" s="58">
         <f>E5-F5</f>
-        <v>27513.365040000001</v>
+        <v>288499.71267936</v>
       </c>
       <c r="H5" s="61">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>2311.1226633600004</v>
+        <v>24233.975865066241</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>258675.22497600003</v>
+        <v>60480</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2413,10 +2290,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>288499.71267936</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>373213.68854442623</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2430,23 +2307,26 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>28550.575230000002</v>
-      </c>
-      <c r="F6" s="71"/>
+        <v>299375.69391132006</v>
+      </c>
+      <c r="F6" s="71">
+        <f>E6</f>
+        <v>299375.69391132006</v>
+      </c>
       <c r="G6" s="58">
         <f t="shared" ref="G6:G8" si="0">E6-F6</f>
-        <v>28550.575230000002</v>
+        <v>0</v>
       </c>
       <c r="H6" s="61">
         <f t="shared" ref="H6:H10" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>2398.2483193200005</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>268426.87036200007</v>
+        <v>62760.000000000007</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2454,10 +2334,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>299375.69391132006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>62760.000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2471,15 +2351,14 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>28787.131940000003</v>
+        <v>270650.92983600002</v>
       </c>
       <c r="F7" s="71">
-        <f t="shared" ref="F7:F10" si="2">E7</f>
-        <v>28787.131940000003</v>
+        <v>270651</v>
       </c>
       <c r="G7" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7.0163999975193292E-2</v>
       </c>
       <c r="H7" s="61">
         <f t="shared" si="1"/>
@@ -2490,18 +2369,18 @@
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>270650.92983600002</v>
+        <v>63280</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
         <v>0</v>
       </c>
       <c r="L7" s="32">
-        <f t="shared" ref="L7:L9" si="3">J7+K7+H7+G7</f>
-        <v>270650.92983600002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" ref="L7:L9" si="2">J7+K7+H7+G7</f>
+        <v>63279.929836000025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2515,11 +2394,11 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>36029.406600000002</v>
+        <v>338741.36604000005</v>
       </c>
       <c r="F8" s="71">
-        <f t="shared" si="2"/>
-        <v>36029.406600000002</v>
+        <f t="shared" ref="F7:F10" si="3">E8</f>
+        <v>338741.36604000005</v>
       </c>
       <c r="G8" s="58">
         <f t="shared" si="0"/>
@@ -2534,18 +2413,18 @@
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>338741.36604000005</v>
+        <v>79200</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
         <v>0</v>
       </c>
       <c r="L8" s="32">
-        <f t="shared" si="3"/>
-        <v>338741.36604000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>79200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2559,15 +2438,14 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>28969.098640000004</v>
+        <v>272361.74481600005</v>
       </c>
       <c r="F9" s="71">
-        <f t="shared" si="2"/>
-        <v>28969.098640000004</v>
+        <v>272400</v>
       </c>
       <c r="G9" s="58">
         <f>E9-F9</f>
-        <v>0</v>
+        <v>-38.255183999950532</v>
       </c>
       <c r="H9" s="61">
         <f t="shared" si="1"/>
@@ -2578,18 +2456,18 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>272361.74481600005</v>
+        <v>63680</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
         <v>0</v>
       </c>
       <c r="L9" s="32">
-        <f t="shared" si="3"/>
-        <v>272361.74481600005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>63641.744816000049</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2603,15 +2481,14 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>32117.12255</v>
+        <v>301958.84397000005</v>
       </c>
       <c r="F10" s="71">
-        <f t="shared" si="2"/>
-        <v>32117.12255</v>
+        <v>302000</v>
       </c>
       <c r="G10" s="58">
         <f>E10-F10</f>
-        <v>0</v>
+        <v>-41.156029999954626</v>
       </c>
       <c r="H10" s="61">
         <f t="shared" si="1"/>
@@ -2622,7 +2499,7 @@
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>301958.84397000005</v>
+        <v>70600</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2630,10 +2507,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>301958.84397000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>70558.843970000045</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2645,19 +2522,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>181966.7</v>
+        <v>1771588.2912526804</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>125902.75973000002</v>
+        <v>1483168.0599513201</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>56063.940270000006</v>
+        <v>288420.23130136012</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>4709.3709826800005</v>
+        <v>24233.975865066241</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="5"/>
@@ -2665,7 +2542,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="5"/>
-        <v>1710814.9800000002</v>
+        <v>400000</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="5"/>
@@ -2673,27 +2550,27 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>1771588.2912526804</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="129"/>
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>712654.20716642635</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="127"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2713,21 +2590,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="106" t="s">
         <v>69</v>
       </c>
@@ -2736,13 +2613,13 @@
       <c r="D1" s="108"/>
       <c r="E1" s="109"/>
       <c r="F1" s="108"/>
-      <c r="G1" s="130">
+      <c r="G1" s="128">
         <v>4500000</v>
       </c>
-      <c r="H1" s="130"/>
+      <c r="H1" s="128"/>
       <c r="I1" s="110"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2771,7 +2648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2792,7 +2669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2824,7 +2701,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2856,7 +2733,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2888,7 +2765,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -2920,7 +2797,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -2952,7 +2829,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -2984,7 +2861,7 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
@@ -3015,21 +2892,21 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="129"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="127"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
@@ -3047,68 +2924,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="136" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="136"/>
       <c r="F1" s="78"/>
       <c r="G1" s="78"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="139" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="137" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="140"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142">
+      <c r="B2" s="138"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="140">
         <v>565</v>
       </c>
-      <c r="E2" s="143"/>
+      <c r="E2" s="141"/>
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="144" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="131" t="s">
+      <c r="E3" s="129" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="131" t="s">
+      <c r="F3" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="131" t="s">
+      <c r="G3" s="129" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="145"/>
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="143"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="80">
         <v>1</v>
       </c>
@@ -3131,7 +3008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="80">
         <v>2</v>
       </c>
@@ -3154,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="80">
         <v>3</v>
       </c>
@@ -3177,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="80">
         <v>4</v>
       </c>
@@ -3200,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="80">
         <v>5</v>
       </c>
@@ -3223,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="85">
         <v>6</v>
       </c>
@@ -3246,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
         <v>10</v>
       </c>
@@ -3265,12 +3142,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="135"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="131"/>
+      <c r="B12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="133"/>
       <c r="F12" s="78"/>
       <c r="G12" s="78"/>
     </row>
